--- a/Fuzzy_AHP_3_Penilai_v11.xlsx
+++ b/Fuzzy_AHP_3_Penilai_v11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\appSaringPramuka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78424AEA-FE2D-4312-9D1C-05014A0B0B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267FD50E-FFDC-4285-AC84-8F2C58434CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="1" r:id="rId1"/>
@@ -669,8 +669,10 @@
     <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -708,8 +710,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1021,7 +1021,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="39"/>
@@ -1222,7 +1222,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="42" t="s">
         <v>30</v>
       </c>
       <c r="B1" s="39"/>
@@ -1295,22 +1295,22 @@
         <v>Siti Aminah</v>
       </c>
       <c r="C5" s="5">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="D5" s="5">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="E5" s="5">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="F5" s="5">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="G5" s="5">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="H5" s="5">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1548,7 +1548,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>31</v>
       </c>
       <c r="B1" s="39"/>
@@ -1621,22 +1621,22 @@
         <v>Siti Aminah</v>
       </c>
       <c r="C5" s="5">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="D5" s="5">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="E5" s="5">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5">
-        <v>85</v>
+        <v>3</v>
       </c>
       <c r="G5" s="5">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1874,7 +1874,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="39"/>
@@ -1947,22 +1947,22 @@
         <v>Siti Aminah</v>
       </c>
       <c r="C5" s="5">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="D5" s="5">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="E5" s="5">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="F5" s="5">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="G5" s="5">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="H5" s="5">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -2200,7 +2200,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="39"/>
@@ -2212,7 +2212,7 @@
       <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="45" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="39"/>
@@ -2292,27 +2292,27 @@
       </c>
       <c r="C6" s="13">
         <f>AVERAGE('Penilai 1'!C5,'Penilai 2'!C5,'Penilai 3'!C5)</f>
-        <v>80</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="D6" s="13">
         <f>AVERAGE('Penilai 1'!D5,'Penilai 2'!D5,'Penilai 3'!D5)</f>
-        <v>82.333333333333329</v>
+        <v>4</v>
       </c>
       <c r="E6" s="13">
         <f>AVERAGE('Penilai 1'!E5,'Penilai 2'!E5,'Penilai 3'!E5)</f>
-        <v>82.666666666666671</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="F6" s="13">
         <f>AVERAGE('Penilai 1'!F5,'Penilai 2'!F5,'Penilai 3'!F5)</f>
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="G6" s="13">
         <f>AVERAGE('Penilai 1'!G5,'Penilai 2'!G5,'Penilai 3'!G5)</f>
-        <v>80</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="H6" s="13">
         <f>AVERAGE('Penilai 1'!H5,'Penilai 2'!H5,'Penilai 3'!H5)</f>
-        <v>79.333333333333329</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -2598,7 +2598,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>35</v>
       </c>
       <c r="B1" s="39"/>
@@ -2613,15 +2613,15 @@
       <c r="K1" s="39"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="14"/>
@@ -2813,15 +2813,15 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
     </row>
     <row r="13" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
@@ -2926,15 +2926,15 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="20" t="s">
@@ -3064,12 +3064,12 @@
       <c r="A35" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B35" s="49" t="str">
+      <c r="B35" s="51" t="str">
         <f>IF(B34&lt;=0.1,"KONSISTEN","TIDAK KONSISTEN")</f>
         <v>KONSISTEN</v>
       </c>
-      <c r="C35" s="50"/>
-      <c r="D35" s="51"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3093,7 +3093,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>49</v>
       </c>
       <c r="B1" s="39"/>
@@ -3117,27 +3117,27 @@
       <c r="T1" s="39"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
       <c r="X3" t="s">
         <v>51</v>
       </c>
@@ -3153,32 +3153,32 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="58" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="39"/>
       <c r="D4" s="39"/>
-      <c r="E4" s="56" t="s">
+      <c r="E4" s="58" t="s">
         <v>7</v>
       </c>
       <c r="F4" s="39"/>
       <c r="G4" s="39"/>
-      <c r="H4" s="56" t="s">
+      <c r="H4" s="58" t="s">
         <v>9</v>
       </c>
       <c r="I4" s="39"/>
       <c r="J4" s="39"/>
-      <c r="K4" s="56" t="s">
+      <c r="K4" s="58" t="s">
         <v>11</v>
       </c>
       <c r="L4" s="39"/>
       <c r="M4" s="39"/>
-      <c r="N4" s="56" t="s">
+      <c r="N4" s="58" t="s">
         <v>13</v>
       </c>
       <c r="O4" s="39"/>
       <c r="P4" s="39"/>
-      <c r="Q4" s="56" t="s">
+      <c r="Q4" s="58" t="s">
         <v>15</v>
       </c>
       <c r="R4" s="39"/>
@@ -3814,27 +3814,27 @@
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="58"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="60"/>
+      <c r="M13" s="60"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="60"/>
+      <c r="P13" s="60"/>
+      <c r="Q13" s="60"/>
+      <c r="R13" s="60"/>
+      <c r="S13" s="60"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
@@ -4096,30 +4096,30 @@
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A33" s="54" t="s">
+      <c r="A33" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="55"/>
-      <c r="J33" s="55"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="55"/>
-      <c r="N33" s="55"/>
-      <c r="O33" s="55"/>
-      <c r="P33" s="55"/>
-      <c r="Q33" s="55"/>
-      <c r="R33" s="55"/>
-      <c r="S33" s="55"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="57"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="57"/>
+      <c r="O33" s="57"/>
+      <c r="P33" s="57"/>
+      <c r="Q33" s="57"/>
+      <c r="R33" s="57"/>
+      <c r="S33" s="57"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A34" s="43" t="s">
+      <c r="A34" s="45" t="s">
         <v>65</v>
       </c>
       <c r="B34" s="39"/>
@@ -4500,7 +4500,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="39"/>
@@ -4512,7 +4512,7 @@
       <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="40" t="s">
         <v>75</v>
       </c>
       <c r="B2" s="39"/>
@@ -4524,7 +4524,7 @@
       <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="38" t="s">
         <v>76</v>
       </c>
       <c r="B3" s="39"/>
@@ -4653,19 +4653,19 @@
       </c>
       <c r="C12" s="13">
         <f>IF('Rekap Nilai'!C6&lt;=5,IF('Rekap Nilai'!C6&lt;=1,1,IF('Rekap Nilai'!C6&lt;=2,1,IF('Rekap Nilai'!C6&lt;=3,2,IF('Rekap Nilai'!C6&lt;=4,3,4)))),MAX(0,'Rekap Nilai'!C6-5))*$A$7+IF('Rekap Nilai'!D6&lt;=5,IF('Rekap Nilai'!D6&lt;=1,1,IF('Rekap Nilai'!D6&lt;=2,1,IF('Rekap Nilai'!D6&lt;=3,2,IF('Rekap Nilai'!D6&lt;=4,3,4)))),MAX(0,'Rekap Nilai'!D6-5))*$B$7+IF('Rekap Nilai'!E6&lt;=5,IF('Rekap Nilai'!E6&lt;=1,1,IF('Rekap Nilai'!E6&lt;=2,1,IF('Rekap Nilai'!E6&lt;=3,2,IF('Rekap Nilai'!E6&lt;=4,3,4)))),MAX(0,'Rekap Nilai'!E6-5))*$C$7+IF('Rekap Nilai'!F6&lt;=5,IF('Rekap Nilai'!F6&lt;=1,1,IF('Rekap Nilai'!F6&lt;=2,1,IF('Rekap Nilai'!F6&lt;=3,2,IF('Rekap Nilai'!F6&lt;=4,3,4)))),MAX(0,'Rekap Nilai'!F6-5))*$D$7+IF('Rekap Nilai'!G6&lt;=5,IF('Rekap Nilai'!G6&lt;=1,1,IF('Rekap Nilai'!G6&lt;=2,1,IF('Rekap Nilai'!G6&lt;=3,2,IF('Rekap Nilai'!G6&lt;=4,3,4)))),MAX(0,'Rekap Nilai'!G6-5))*$E$7+IF('Rekap Nilai'!H6&lt;=5,IF('Rekap Nilai'!H6&lt;=1,1,IF('Rekap Nilai'!H6&lt;=2,1,IF('Rekap Nilai'!H6&lt;=3,2,IF('Rekap Nilai'!H6&lt;=4,3,4)))),MAX(0,'Rekap Nilai'!H6-5))*$F$7</f>
-        <v>76.394226705878879</v>
+        <v>18.583702712025982</v>
       </c>
       <c r="D12" s="13">
         <f>IF('Rekap Nilai'!C6&lt;=5,IF('Rekap Nilai'!C6&lt;=1,1,IF('Rekap Nilai'!C6&lt;=2,2,IF('Rekap Nilai'!C6&lt;=3,3,IF('Rekap Nilai'!C6&lt;=4,4,5)))),'Rekap Nilai'!C6)*$A$7+IF('Rekap Nilai'!D6&lt;=5,IF('Rekap Nilai'!D6&lt;=1,1,IF('Rekap Nilai'!D6&lt;=2,2,IF('Rekap Nilai'!D6&lt;=3,3,IF('Rekap Nilai'!D6&lt;=4,4,5)))),'Rekap Nilai'!D6)*$B$7+IF('Rekap Nilai'!E6&lt;=5,IF('Rekap Nilai'!E6&lt;=1,1,IF('Rekap Nilai'!E6&lt;=2,2,IF('Rekap Nilai'!E6&lt;=3,3,IF('Rekap Nilai'!E6&lt;=4,4,5)))),'Rekap Nilai'!E6)*$C$7+IF('Rekap Nilai'!F6&lt;=5,IF('Rekap Nilai'!F6&lt;=1,1,IF('Rekap Nilai'!F6&lt;=2,2,IF('Rekap Nilai'!F6&lt;=3,3,IF('Rekap Nilai'!F6&lt;=4,4,5)))),'Rekap Nilai'!F6)*$D$7+IF('Rekap Nilai'!G6&lt;=5,IF('Rekap Nilai'!G6&lt;=1,1,IF('Rekap Nilai'!G6&lt;=2,2,IF('Rekap Nilai'!G6&lt;=3,3,IF('Rekap Nilai'!G6&lt;=4,4,5)))),'Rekap Nilai'!G6)*$E$7+IF('Rekap Nilai'!H6&lt;=5,IF('Rekap Nilai'!H6&lt;=1,1,IF('Rekap Nilai'!H6&lt;=2,2,IF('Rekap Nilai'!H6&lt;=3,3,IF('Rekap Nilai'!H6&lt;=4,4,5)))),'Rekap Nilai'!H6)*$F$7</f>
-        <v>81.394226705878864</v>
+        <v>20.328070728046107</v>
       </c>
       <c r="E12" s="13">
         <f>IF('Rekap Nilai'!C6&lt;=5,IF('Rekap Nilai'!C6&lt;=1,2,IF('Rekap Nilai'!C6&lt;=2,3,IF('Rekap Nilai'!C6&lt;=3,4,IF('Rekap Nilai'!C6&lt;=4,5,5)))),MIN(100,'Rekap Nilai'!C6+5))*$A$7+IF('Rekap Nilai'!D6&lt;=5,IF('Rekap Nilai'!D6&lt;=1,2,IF('Rekap Nilai'!D6&lt;=2,3,IF('Rekap Nilai'!D6&lt;=3,4,IF('Rekap Nilai'!D6&lt;=4,5,5)))),MIN(100,'Rekap Nilai'!D6+5))*$B$7+IF('Rekap Nilai'!E6&lt;=5,IF('Rekap Nilai'!E6&lt;=1,2,IF('Rekap Nilai'!E6&lt;=2,3,IF('Rekap Nilai'!E6&lt;=3,4,IF('Rekap Nilai'!E6&lt;=4,5,5)))),MIN(100,'Rekap Nilai'!E6+5))*$C$7+IF('Rekap Nilai'!F6&lt;=5,IF('Rekap Nilai'!F6&lt;=1,2,IF('Rekap Nilai'!F6&lt;=2,3,IF('Rekap Nilai'!F6&lt;=3,4,IF('Rekap Nilai'!F6&lt;=4,5,5)))),MIN(100,'Rekap Nilai'!F6+5))*$D$7+IF('Rekap Nilai'!G6&lt;=5,IF('Rekap Nilai'!G6&lt;=1,2,IF('Rekap Nilai'!G6&lt;=2,3,IF('Rekap Nilai'!G6&lt;=3,4,IF('Rekap Nilai'!G6&lt;=4,5,5)))),MIN(100,'Rekap Nilai'!G6+5))*$E$7+IF('Rekap Nilai'!H6&lt;=5,IF('Rekap Nilai'!H6&lt;=1,2,IF('Rekap Nilai'!H6&lt;=2,3,IF('Rekap Nilai'!H6&lt;=3,4,IF('Rekap Nilai'!H6&lt;=4,5,5)))),MIN(100,'Rekap Nilai'!H6+5))*$F$7</f>
-        <v>86.394226705878879</v>
+        <v>21.562188356447706</v>
       </c>
       <c r="F12" s="36">
         <f t="shared" si="0"/>
-        <v>81.394226705878879</v>
+        <v>20.157987265506598</v>
       </c>
       <c r="G12" s="37">
         <f t="shared" si="1"/>
